--- a/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.QA.FRM.04.03. Kuru İşlem Kontrol Formu.xlsx
+++ b/formlar/4. Yıkama Bölümü (ERTELENDİ)/EMS.QA.FRM.04.03. Kuru İşlem Kontrol Formu.xlsx
@@ -278,7 +278,7 @@
 نموذج فحص المعالجة الجافة</t>
   </si>
   <si>
-    <t>EG.QA.FRM.04.03</t>
+    <t>EMS.QA.FRM.04.03</t>
   </si>
 </sst>
 </file>
